--- a/Daily_Paid_Payments_Krishi_Bills_October_2026/Purchase_list_date_17-10-2026 to 23-10-2026/Daily_Paid_List  Details_From_Date_17-10-2026_to_23-10-2026 .pdf.xlsx
+++ b/Daily_Paid_Payments_Krishi_Bills_October_2026/Purchase_list_date_17-10-2026 to 23-10-2026/Daily_Paid_List  Details_From_Date_17-10-2026_to_23-10-2026 .pdf.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\Daily_Paid_Payments_Krishi_Bills_October_2026\Purchase_list_date_17-10-2026 to 23-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C88B375-E7B8-4277-8AFA-134330730DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55C2040-2CE5-42FE-8D2A-B92011B08528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{803B6BBC-987E-491C-8826-B9BF16D0AB39}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>M/S KRISHI INFRATECH,SOMPETA</t>
   </si>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>Disti Bommalu Big size 2 No's for Camp office.</t>
-  </si>
-  <si>
-    <t>267</t>
   </si>
   <si>
     <t>Disti Bommalu Big size 1 No's for crusher</t>
@@ -304,9 +301,6 @@
   <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -402,6 +396,9 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -730,58 +727,58 @@
     <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3">
         <v>3491</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>3491</v>
       </c>
     </row>
@@ -792,15 +789,15 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="6"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>169</v>
       </c>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6">
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
         <f>G4-E5+F5</f>
         <v>3322</v>
       </c>
@@ -812,362 +809,354 @@
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6"/>
+      <c r="C6" s="5"/>
       <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>360</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6">
-        <f t="shared" ref="G6:G18" si="0">G5-E6+F6</f>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5">
+        <f t="shared" ref="G6:G19" si="0">G5-E6+F6</f>
         <v>2962</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="6">
-        <v>180</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5">
         <f t="shared" si="0"/>
-        <v>2782</v>
+        <v>2962</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>396102</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="6">
+        <v>17</v>
+      </c>
+      <c r="E8" s="5">
         <v>229</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6">
+      <c r="F8" s="5"/>
+      <c r="G8" s="5">
         <f t="shared" si="0"/>
-        <v>2553</v>
+        <v>2733</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>94</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="6">
+        <v>19</v>
+      </c>
+      <c r="E9" s="5">
         <v>3000</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6">
+      <c r="F9" s="5"/>
+      <c r="G9" s="5">
         <f t="shared" si="0"/>
-        <v>-447</v>
+        <v>-267</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>95</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="6">
+        <v>21</v>
+      </c>
+      <c r="E10" s="5">
         <v>350</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6">
+      <c r="F10" s="5"/>
+      <c r="G10" s="5">
         <f t="shared" si="0"/>
-        <v>-797</v>
+        <v>-617</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="6"/>
+      <c r="C11" s="5"/>
       <c r="D11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6">
+        <v>23</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5">
         <v>1000</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <f t="shared" si="0"/>
-        <v>203</v>
+        <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6">
+        <v>25</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5">
         <v>2000</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <f t="shared" si="0"/>
-        <v>2203</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>265</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6">
+      <c r="F13" s="5"/>
+      <c r="G13" s="5">
         <f t="shared" si="0"/>
-        <v>1938</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="5"/>
+      <c r="D14" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="6">
+      <c r="E14" s="5">
         <v>2000</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6">
+      <c r="F14" s="5"/>
+      <c r="G14" s="5">
         <f t="shared" si="0"/>
-        <v>-62</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C15" s="6"/>
+        <v>31</v>
+      </c>
+      <c r="C15" s="5"/>
       <c r="D15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6">
+        <v>23</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5">
         <v>2000</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <f t="shared" si="0"/>
-        <v>1938</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="D16" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="5">
+        <v>1790</v>
+      </c>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5">
+        <f t="shared" si="0"/>
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>277</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5">
+        <v>7000</v>
+      </c>
+      <c r="G17" s="5">
+        <f t="shared" si="0"/>
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5">
+        <f t="shared" si="0"/>
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5">
+        <f t="shared" si="0"/>
+        <v>7328</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E16" s="6">
-        <v>1790</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6">
-        <f t="shared" si="0"/>
-        <v>148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>277</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6">
-        <v>7000</v>
-      </c>
-      <c r="G17" s="6">
-        <f t="shared" si="0"/>
-        <v>7148</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6">
-        <f t="shared" si="0"/>
-        <v>7148</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6">
-        <f>G18-E19+F19</f>
-        <v>7148</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="9">
+      <c r="E20" s="8">
         <f>SUM(E5:E18)</f>
-        <v>8343</v>
-      </c>
-      <c r="F20" s="9">
+        <v>8163</v>
+      </c>
+      <c r="F20" s="8">
         <f>SUM(F4:F16)</f>
         <v>8491</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <f>G19-E19+F19</f>
-        <v>7148</v>
+        <v>7328</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="14"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="15"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="G22" s="17"/>
+      <c r="A22" s="14"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="G22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="20" t="s">
+      <c r="A23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="21"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="22" t="s">
         <v>40</v>
-      </c>
-      <c r="E23" s="21"/>
-      <c r="F23" s="21"/>
-      <c r="G23" s="22"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="7"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="23" t="s">
-        <v>41</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
-      <c r="G24" s="10"/>
+      <c r="G24" s="9"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="24">
-        <v>7148</v>
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="23">
+        <v>7328</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -1179,56 +1168,56 @@
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1">
         <v>180</v>
       </c>
-      <c r="F27" s="6"/>
-      <c r="G27" s="26">
+      <c r="F27" s="5"/>
+      <c r="G27" s="25">
         <f>G26-E27+F27</f>
-        <v>6968</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="26">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="25">
         <f t="shared" ref="G28:G29" si="1">G27-E28+F28</f>
-        <v>6968</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="29"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="26">
+      <c r="A29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="25">
         <f t="shared" si="1"/>
-        <v>6968</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="29"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="35"/>
-      <c r="D30" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="36">
+      <c r="A30" s="28"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="35">
         <f>SUM(E27:E29)</f>
         <v>180</v>
       </c>
-      <c r="F30" s="36"/>
-      <c r="G30" s="9">
+      <c r="F30" s="35"/>
+      <c r="G30" s="8">
         <f>G29-E29+F29</f>
-        <v>6968</v>
+        <v>7148</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
